--- a/www/download/COUNTRY.LTU.zdW13.xlsx
+++ b/www/download/COUNTRY.LTU.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Lituânia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.99999999710861</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.00000001825342</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.99999998659746</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.9999999995881</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.99999999559562</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.99999999588469</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.99999999905712</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.6655545966935</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.05558102643111</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.77785491279575</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.76969939037289</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.74982120464169</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.52016123792344</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.34585943266422</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.47782342361756</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.59610272422646</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.44594282480374</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1.47599318357159</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.976940312088795</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>0.893393417392551</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>0.927598057496928</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.346</t>
+          <t>0.991380526723325</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>0.908832260562732</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>0.834690735610148</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>1.08274539924991</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.08684210035247</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.03143132201443</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.2387591957267</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.06357079173401</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1.13252914924912</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>3.48828822280141</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>3.22840787512189</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>3.28371127379246</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>2.66979135618004</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>2.53960382783567</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>2.49513979280171</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>2.50815727999988</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.113</t>
+          <t>2.4347870808855</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>2.04007192735548</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>2.59636682747891</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>2.55663741023707</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>2.45318296452318</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>2.6076510411879</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>2.39165540097397</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>2.59473843571827</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2571.545</t>
+          <t>4.53265282243995</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2595.514</t>
+          <t>4.09053351773152</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2602.912</t>
+          <t>4.08308806834813</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2659.424</t>
+          <t>3.50140311154743</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2522.551</t>
+          <t>3.43859169174989</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2583.224</t>
+          <t>3.3854495070012</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2464.605</t>
+          <t>3.28700492714821</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2513.641</t>
+          <t>3.22843801127306</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2546.154</t>
+          <t>2.10141111214789</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2578.763</t>
+          <t>3.35943149855283</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2732.644</t>
+          <t>3.28978371019045</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2760.572</t>
+          <t>3.13195758889831</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2868.389</t>
+          <t>2.5755476008327</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2915.074</t>
+          <t>2.11600501393159</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2692.609</t>
+          <t>2.19137955641329</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2087.973</t>
+          <t>2976105427.1958</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1988.28</t>
+          <t>2930063990.15321</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1990.438</t>
+          <t>2636634010.2104</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2076.019</t>
+          <t>2821328470.98746</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2016.758</t>
+          <t>2635078102.13662</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2079.554</t>
+          <t>2708607390.92052</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1980.536</t>
+          <t>2637935396.5157</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2019.223</t>
+          <t>2669120596.62752</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2053.925</t>
+          <t>2772783808.7137</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2112.124</t>
+          <t>2658309601.11984</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2274.689</t>
+          <t>2783949930.77216</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2341.042</t>
+          <t>2749480786.89653</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2475.446</t>
+          <t>2804401292.36203</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2553.702</t>
+          <t>2949136757.28203</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2306.659</t>
+          <t>2505781910.51527</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>557782210.864289</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>567178594.45442</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>558319827.667075</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>689433446.125028</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>695116687.694561</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>721241290.640308</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>680165990.535796</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>714810956.595207</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>807486328.883768</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>714756054.651508</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>779978485.951183</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>826143349.90051</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>830691008.580721</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>929700249.203293</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>813598869.140455</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>7025953.64037786</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>5726733.65375848</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>56.27</t>
+          <t>4796919.23785121</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56.54</t>
+          <t>4469483.56703429</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>4539484.74308696</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>4428280.35225316</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>4035894.45416913</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>3585829.74870999</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>2922920.64572953</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>2277547.50934983</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>2063594.14705121</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>1800003.28174383</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>1476252.91727832</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>1253266.43648018</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>1440121.41395777</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>15028.2390925972</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>15215.8253999373</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>14696.9413391798</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>15290.8481334126</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>14975.8321912235</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>15496.0228024728</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>14324.2676312429</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>14680.1721388314</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>16093.6877497649</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>17477.5523476409</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>19710.3299616258</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>20150.0964480615</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>23402.399299415</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>24829.6562805292</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>21176.7336637414</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>25643.5189113818</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.21</t>
+          <t>25427.5151098798</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>22807.6795942686</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24159.1479033289</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23470.5786546861</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>24524.4502077631</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>23196.2148573609</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>23982.7699205988</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>26708.917553651</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>28164.6456689691</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>31591.727494781</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>32572.2347538057</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>37433.5132412234</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>43097.9266279286</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>34136.1623034002</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>64.62</t>
+          <t>2.74334813719617</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>2.50556247968519</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>65.31</t>
+          <t>2.56504981798156</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>2.01119518633754</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>1.90132295153037</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>67.09</t>
+          <t>1.88329859505659</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>1.91184254731119</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.81</t>
+          <t>1.82483534467417</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>65.69</t>
+          <t>1.54360343516806</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>1.9550277415928</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>1.91634838777126</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>1.83369924211977</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>62.39</t>
+          <t>1.97998410290901</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>1.74680140693664</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>1.83513021648075</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.99999999710861</t>
+          <t>463.81357963104</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.00000001825342</t>
+          <t>493.499168584721</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.99999998659746</t>
+          <t>486.256599605534</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.9999999995881</t>
+          <t>581.064851348527</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.99999999559562</t>
+          <t>596.717905137403</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.99999999588469</t>
+          <t>641.787943264201</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.99999999905712</t>
+          <t>630.659240181545</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.6655545966935</t>
+          <t>642.295764754432</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05558102643111</t>
+          <t>712.634656150179</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.77785491279575</t>
+          <t>616.807088929503</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.76969939037289</t>
+          <t>644.237619518612</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.74982120464169</t>
+          <t>659.806205495176</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.52016123792344</t>
+          <t>629.740738822471</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.34585943266422</t>
+          <t>691.844209855107</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.47782342361756</t>
+          <t>654.2827523398</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-166259978.893008</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-170853832.582568</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-176077430.208719</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-162340115.850965</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-49253178.7636012</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>55914847.9623841</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>95737376.8490772</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>104107944.219319</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>191295585.675191</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>76594357.4705027</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>72561037.5460365</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>63653487.4822625</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>5165169.32419016</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>189803193.784872</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>263473302.191596</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-212232747.988109</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-222344140.088472</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-234770360.737617</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-214910332.086852</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-93658173.3059009</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-2341074.09891468</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>18190555.4134069</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2159452.09417736</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>69401835.8036734</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-40202293.147875</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-79809986.0473379</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-105533011.65154</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-216242250.120786</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-3301442.96548029</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>45260272.8418897</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>45972769.0951012</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>51490307.5059037</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>58692930.5288979</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>52570216.2358875</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>44404994.5422997</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>58255922.0612988</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>77546821.4356702</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>101948492.125142</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>121893749.871518</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>116796650.618378</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>152371023.593374</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>169186499.133803</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>221407419.444976</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>193104636.750352</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>218213029.349706</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1736.21569931814</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1729.99216914644</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1733.52900191604</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1749.69968333062</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1731.27135376427</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1850.46627513792</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1836.38040841557</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1814.37977801284</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1812.65995940341</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1822.68205899778</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1878.8213430247</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1869.69234445761</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1876.61739064514</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1900.35864901098</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>1854.97680128076</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1737.2956357249</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1737.87321085869</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1732.38735440932</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1784.36929683306</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1731.09456491902</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1846.21497998856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1831.19451292704</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1802.02217524244</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1785.64695981485</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1809.02350052613</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1870.77732792535</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1855.72164497361</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1876.11289162143</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1904.35279196967</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1866.1323893281</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>159.61</t>
+          <t>2785.35475277992</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>144.59</t>
+          <t>3540.9300159829</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>4435.34973971317</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>4160.90500981388</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>89.34</t>
+          <t>3524.99083892768</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>92.76</t>
+          <t>4403.01337789616</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>99.14</t>
+          <t>5178.13508376535</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>90.88</t>
+          <t>5887.63000237662</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>83.47</t>
+          <t>7706.11485602183</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>108.27</t>
+          <t>9118.8685379579</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>12140.3079666271</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>14416.2990549895</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>123.88</t>
+          <t>17142.913254606</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>106.36</t>
+          <t>23876.027783493</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>113.25</t>
+          <t>17610.1738120431</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>348.83</t>
+          <t>682424167.307582</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>322.84</t>
+          <t>662253634.440673</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>328.37</t>
+          <t>670327250.202698</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>266.98</t>
+          <t>640128255.626884</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>253.96</t>
+          <t>567551860.799558</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>249.51</t>
+          <t>653229941.649899</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>250.82</t>
+          <t>688200694.90741</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>243.48</t>
+          <t>697167141.482642</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>204.01</t>
+          <t>748541629.399584</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>259.64</t>
+          <t>631345780.987496</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>255.66</t>
+          <t>749087322.276852</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>245.32</t>
+          <t>766710676.39237</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>260.77</t>
+          <t>761398941.866016</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>239.17</t>
+          <t>855542342.606963</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>259.47</t>
+          <t>757123817.465011</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>453.27</t>
+          <t>3526.51382046901</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>409.05</t>
+          <t>4409.395665596</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>408.31</t>
+          <t>5563.63210469451</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>350.14</t>
+          <t>5658.86379586788</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>343.86</t>
+          <t>4855.91104604275</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>338.54</t>
+          <t>5338.12529778591</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>328.7</t>
+          <t>6119.8313817904</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>322.84</t>
+          <t>7063.11434683333</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>210.14</t>
+          <t>9191.95625324947</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>335.94</t>
+          <t>11091.372515054</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>328.98</t>
+          <t>14441.4051098642</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>313.2</t>
+          <t>17761.9081874317</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>257.55</t>
+          <t>22277.3042327746</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>211.6</t>
+          <t>29376.4381969645</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>219.14</t>
+          <t>18317.813610085</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2571.545</t>
+          <t>618310157.436481</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2595.514</t>
+          <t>606200914.446445</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2602.912</t>
+          <t>630780847.846882</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2659.424</t>
+          <t>670057676.888039</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2522.551</t>
+          <t>693146231.629646</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2583.224</t>
+          <t>833532264.066674</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2464.605</t>
+          <t>915916225.750916</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2513.641</t>
+          <t>964190874.27809</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2546.154</t>
+          <t>1135484031.54985</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2578.763</t>
+          <t>946803493.565628</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2732.644</t>
+          <t>1079720890.58875</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2760.572</t>
+          <t>1173548776.63155</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2868.389</t>
+          <t>1232699627.85218</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2915.074</t>
+          <t>1494911774.08483</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2692.609</t>
+          <t>1084293004.23577</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2087.973</t>
+          <t>-741.15906768909</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1988.28</t>
+          <t>-868.465649613101</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1990.438</t>
+          <t>-1128.28236498135</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2076.019</t>
+          <t>-1497.958786054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2016.758</t>
+          <t>-1330.92020711507</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2079.554</t>
+          <t>-935.11191988976</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1980.536</t>
+          <t>-941.696298025052</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2019.223</t>
+          <t>-1175.48434445671</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2053.925</t>
+          <t>-1485.84139722765</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2112.124</t>
+          <t>-1972.50397709605</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2274.689</t>
+          <t>-2301.09714323712</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2341.042</t>
+          <t>-3345.60913244218</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2475.446</t>
+          <t>-5134.39097816862</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2553.702</t>
+          <t>-5500.41041347152</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2306.659</t>
+          <t>-707.639798041871</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2976.105</t>
+          <t>64114009.8711008</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2930.064</t>
+          <t>56052719.9942279</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2636.634</t>
+          <t>39546402.3558156</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2821.328</t>
+          <t>-29929421.2611549</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2635.078</t>
+          <t>-125594370.830088</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2708.607</t>
+          <t>-180302322.416775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2637.935</t>
+          <t>-227715530.843506</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2669.121</t>
+          <t>-267023732.795447</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2772.784</t>
+          <t>-386942402.150268</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2658.31</t>
+          <t>-315457712.578132</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2783.95</t>
+          <t>-330633568.311894</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2749.481</t>
+          <t>-406838100.239184</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2804.401</t>
+          <t>-471300685.986166</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2949.137</t>
+          <t>-639369431.477866</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2505.782</t>
+          <t>-327169186.770756</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>3247.55</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>4107.62498</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>4884.125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>5344.84999</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>5082.15008</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>5179.55</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>5518.45004</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>6309.08615</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>8480.41658</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>10617.22104</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>12152.58224</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>13964.39876</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>17812.98732</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>21228.38204</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>15968.43085</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1744.13</t>
+          <t>0.125373949026756</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1753.35</t>
+          <t>0.11497645531624</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1699.009</t>
+          <t>0.132894733979261</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1785.68</t>
+          <t>0.136782404368877</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1681.36</t>
+          <t>0.133312486343629</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1711.461</t>
+          <t>0.152782492842231</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1628.994</t>
+          <t>0.15904113089427</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1633.804</t>
+          <t>0.166951404668162</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1670.765</t>
+          <t>0.175434236104611</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1649.612</t>
+          <t>0.177465430372395</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1736.928</t>
+          <t>0.181637176841599</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1700.906</t>
+          <t>0.175054743950889</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1753.234</t>
+          <t>0.170483416095847</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1699.062</t>
+          <t>0.161259511278282</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1554.489</t>
+          <t>0.141327322564836</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2504.97500744375</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3185.72497070167</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3915.82503481901</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4674.57499957807</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4707.72500997286</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4508.299991816</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>4631.35001721752</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>5473.03260370754</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>7280.6121051987</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9086.21960703123</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>10621.4053437327</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>12904.6207284722</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>16887.3322519144</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>21323.5323202352</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>16682.5566681587</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>557.782</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>567.179</t>
+          <t>4413.2116762702</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>558.32</t>
+          <t>4810.78304557858</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>689.433</t>
+          <t>5513.89748690017</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>695.117</t>
+          <t>5373.96564117383</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>721.241</t>
+          <t>5163.52928834904</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>680.166</t>
+          <t>5423.21665241783</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>714.811</t>
+          <t>6355.59458427306</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>807.486</t>
+          <t>8402.73777334017</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>714.756</t>
+          <t>10486.1630721106</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>779.978</t>
+          <t>12126.7510595509</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>826.143</t>
+          <t>14490.2804927815</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>830.691</t>
+          <t>19059.9184852712</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>929.7</t>
+          <t>23934.7048099527</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>813.599</t>
+          <t>18804.4211754875</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>274.33</t>
+          <t>24600.7898997101</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>250.56</t>
+          <t>27546.6244373116</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>256.5</t>
+          <t>30603.485199467</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201.12</t>
+          <t>31813.1379045267</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>190.13</t>
+          <t>32026.7029437954</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>188.33</t>
+          <t>32640.4917139336</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>191.18</t>
+          <t>33887.0412155523</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>182.48</t>
+          <t>37548.8012106701</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>154.36</t>
+          <t>47207.3276034981</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>55893.2189614342</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>191.63</t>
+          <t>62765.6060762895</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>183.37</t>
+          <t>72359.252719093</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>93978.2073332064</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>174.68</t>
+          <t>115669.457151328</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>183.51</t>
+          <t>102329.524978285</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.026</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.727</t>
+          <t>3647.69272428469</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4.797</t>
+          <t>3627.32457554207</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.469</t>
+          <t>3993.82412836323</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.539</t>
+          <t>3970.65942851008</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.428</t>
+          <t>3851.35197013299</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.036</t>
+          <t>4095.94484300415</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.586</t>
+          <t>4385.76814554866</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.923</t>
+          <t>4887.15773120033</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.278</t>
+          <t>5340.7093261259</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.064</t>
+          <t>5713.95903946836</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6311.66165310784</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>7067.72863079353</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>7387.65518169046</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>6483.95376910765</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2504.97500744375</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2657.11121643758</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2939.42878253037</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3329.00648439264</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3412.31095538772</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3237.98370956394</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3330.82440010191</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3612.69539104058</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>4043.94705554353</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>4417.79952482758</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>4874.89543464886</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5542.76286926896</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6135.93360606634</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6441.95147274622</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>5475.74598192922</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3084.29817890418</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3167.2132337298</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4067.04202442142</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4351.47749309983</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4269.55939882617</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4986.89569165096</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5389.43335758217</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6268.82510572694</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8281.78145665983</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>9919.11415788945</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11400.5674904491</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12666.8304572185</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16021.7258247288</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>18652.8001300473</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14461.9577845125</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2087973000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1988280000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1990438000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2076018674.27178</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2016758000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2079554000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1980536270.47619</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2019223254.9505</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2053925000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2112123969.96663</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2274689000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2341041784.49537</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2475446000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2553701952.54095</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2306658737.99467</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2571545000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2595513640.41746</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2602912000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2659424000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2522551000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2583224000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2464604694.9485</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2513640732.24568</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2546154000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2578763000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2732644442.90056</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2760571519.06275</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2868389000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2915073729.0729</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2692608724.27263</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1744129738.17035</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1753350332.98209</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1699009108.78661</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1785679915.40786</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1681359801.51844</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1711461074.03315</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1628993904.65116</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1633804183.06636</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1670764707.15835</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1649612274.76038</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1736928496.27263</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1700905800.8089</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1753234285.45781</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1699062060.21834</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1554488629.00202</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1480200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1493500</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1502500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1490400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1457200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1399200</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1345900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1394900</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1425900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1425500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1460700</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1487600</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1528900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1530742.48708814</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1442881.941105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1202600</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1149300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1148200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1186500</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1164900</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1123800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1078500</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1112900</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1133100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1158800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1210700</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1252100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1319100</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1343800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1243497.35069574</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2571545000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2595513640.41746</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2602912000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2659424000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2522551000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2583224000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2464604694.9485</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2513640732.24568</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2546154000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2578763000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2732644442.90056</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2760571519.06275</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2868389000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2915073729.0729</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2692608724.27263</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2087973000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1988280000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1990438000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2076018674.27178</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2016758000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2079554000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1980536270.47619</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2019223254.9505</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2053925000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2112123969.96663</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2274689000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2341041784.49537</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2475446000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2553701952.54095</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2306658737.99467</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.38297454039357</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.374950919159893</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.365446441330267</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.354082269774032</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.344615980455163</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.346596133326365</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.34174830988491</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.345725669120357</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.342606166961938</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.366551899886692</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.379590543195016</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.382423371633458</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.383804148482609</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.391863244594682</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.401402104157042</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.551165908038753</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.56012188209631</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.562656144083645</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.565446055716564</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.58347578064208</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.584354733603416</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.589745862974171</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.587979910136802</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.579241250905231</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.571140274425083</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.562470444100666</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.562069271680628</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.545168024157812</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.543979820692733</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.532984201290888</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0658595515676768</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0649271987437972</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0718974145860885</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0804716745094041</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0719082389027571</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0690491330702188</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0685058271409187</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0662944207428411</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0781525821328311</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0623078256882247</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0579390127043173</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0555073566859132</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0710278273595789</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0641569347125852</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0656136945520701</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.266277538684155</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.262117929860927</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.253299215853023</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.244044451439439</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.23726177005492</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.239032304805718</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.239857012683979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.246429012006655</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.263919508581308</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.26640937752232</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.278650240628368</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.283375972739592</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.297986422791148</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.304431719963992</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.317696418422825</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.646228047280277</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.652627353480906</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.653107348417245</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.652594632124127</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.670062556504154</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.670949445669624</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.671623283553242</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.668130510696502</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.656894682280306</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.65300956755162</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.646707543985714</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.644679842235686</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.623911083320607</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.633630615149237</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.623970896490178</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0874944140355671</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0852547166581675</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0935934357297325</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.103360916436434</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0926756734409259</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0900182495246576</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0885197037627784</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0854404772968434</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0791858091383855</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.08058105492606</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.074642215385918</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0719441850247218</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0781024938882458</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0619376648867707</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0583326850869971</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13012.95002</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>16011.72486</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17948.70002</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>19579.40021</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>18273.80013</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>19248.7999</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20729.19991</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>24205.77749</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>31550.79177</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>38827.22596</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>45762.79956</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>53512.71586</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>68779.84557</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>87380.2149</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>63756.94838</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6015.75001</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7580.42491</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8877.82507</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9865.37498</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9643.52504</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10150.42498</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10812.65001</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>12624.41969</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>16684.51923</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20405.27723</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23527.31855</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>27157.11095</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>35081.64431</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>42587.50494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>33266.37896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>98403.1598270781</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>101377.408978468</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>105819.601650491</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>111683.194777985</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>116521.856497935</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>120126.189828282</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>124588.862428806</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>129644.249343817</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>135812.082947234</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>143521.622402548</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>152146.281960362</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>163093.292643572</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>177643.798404054</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>190049.299326338</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>192823.545110645</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
